--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>AVELLEIRA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
     <t>ABAD</t>
   </si>
   <si>
@@ -97,6 +106,15 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -110,6 +128,15 @@
   </si>
   <si>
     <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
   </si>
   <si>
     <t>MARITZA</t>
@@ -977,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1009,16 +1036,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920331</v>
+        <v>21330051920332</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1032,16 +1059,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920335</v>
+        <v>21330051920149</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1055,22 +1082,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920137</v>
+        <v>20330051920200</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1078,16 +1105,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920336</v>
+        <v>21330051920331</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1096,21 +1123,21 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920340</v>
+        <v>21330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1119,21 +1146,21 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920347</v>
+        <v>21330051920137</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1142,7 +1169,76 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920336</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920340</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920347</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -88,73 +88,166 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ABAD</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECATL</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
     <t>GALVEZ</t>
   </si>
   <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>SOL</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>ISRAEL</t>
   </si>
   <si>
     <t>JOSELIN</t>
   </si>
   <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>YAIR DAVID</t>
+  </si>
+  <si>
+    <t>DARLET VICTORIA</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABET</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
     <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
-    <t>DARLET VICTORIA</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,10 +1135,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1065,10 +1158,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1082,22 +1175,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920200</v>
+        <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1111,10 +1204,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1134,10 +1227,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1157,10 +1250,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1180,10 +1273,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1203,10 +1296,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1226,10 +1319,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1238,6 +1331,282 @@
         <v>10</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920029</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920031</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920035</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920390</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920046</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920057</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920059</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920060</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920062</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920063</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920067</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920200</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -671,10 +671,10 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>17</v>
@@ -683,7 +683,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -837,10 +837,10 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>29</v>
@@ -994,10 +994,10 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>17</v>
@@ -1006,7 +1006,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>6.1</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
   <si>
     <t>Mat</t>
   </si>
@@ -88,7 +88,7 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>COMIHUA</t>
+    <t>LUNA</t>
   </si>
   <si>
     <t>ABAD</t>
@@ -136,18 +136,12 @@
     <t>VEGA</t>
   </si>
   <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
     <t>SOL</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -184,16 +178,13 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
     <t>ISRAEL</t>
   </si>
   <si>
     <t>JOSELIN</t>
   </si>
   <si>
-    <t>ALEJANDRO GABRIEL</t>
+    <t>MIRANDA</t>
   </si>
   <si>
     <t>MARITZA</t>
@@ -245,9 +236,6 @@
   </si>
   <si>
     <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,10 +1123,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,10 +1146,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1175,22 +1163,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920036</v>
+        <v>20330051920273</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1204,10 +1192,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1227,10 +1215,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1250,10 +1238,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1273,10 +1261,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1296,10 +1284,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1319,10 +1307,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1342,10 +1330,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1365,10 +1353,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1388,10 +1376,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1411,10 +1399,10 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1434,10 +1422,10 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1457,10 +1445,10 @@
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1480,10 +1468,10 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1503,10 +1491,10 @@
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1529,7 +1517,7 @@
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1549,10 +1537,10 @@
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1572,10 +1560,10 @@
         <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1584,29 +1572,6 @@
         <v>11</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920200</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="66">
   <si>
     <t>Mat</t>
   </si>
@@ -88,9 +88,6 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>ABAD</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -163,15 +157,9 @@
     <t>CELESTINO</t>
   </si>
   <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -184,9 +172,6 @@
     <t>JOSELIN</t>
   </si>
   <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
     <t>MARITZA</t>
   </si>
   <si>
@@ -217,16 +202,10 @@
     <t>KARLA JIMENA</t>
   </si>
   <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
@@ -662,10 +641,10 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -674,7 +653,7 @@
         <v>40</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -828,16 +807,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>46.67</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -874,16 +856,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>70.59</v>
+      </c>
+      <c r="H5">
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -897,16 +882,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H6">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -985,19 +973,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>46.67</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1040,16 +1028,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1066,16 +1054,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>89.47</v>
+        <v>78.95</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1085,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,10 +1111,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,10 +1134,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1163,39 +1151,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920273</v>
+        <v>21330051920331</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920331</v>
+        <v>21330051920335</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1209,16 +1197,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920335</v>
+        <v>21330051920137</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1232,16 +1220,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920137</v>
+        <v>21330051920336</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1255,16 +1243,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920336</v>
+        <v>21330051920340</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1278,16 +1266,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920340</v>
+        <v>21330051920347</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1301,22 +1289,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920347</v>
+        <v>21330051920029</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1324,16 +1312,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920029</v>
+        <v>21330051920031</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1347,16 +1335,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920031</v>
+        <v>21330051920035</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1370,16 +1358,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920035</v>
+        <v>21330051920390</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1393,16 +1381,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920390</v>
+        <v>21330051920057</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1416,16 +1404,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920046</v>
+        <v>21330051920059</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1439,16 +1427,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920057</v>
+        <v>21330051920062</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1462,16 +1450,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920059</v>
+        <v>21330051920063</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1485,16 +1473,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920060</v>
+        <v>21330051920067</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1503,75 +1491,6 @@
         <v>11</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920062</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920063</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920067</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -88,6 +88,12 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
     <t>ABAD</t>
   </si>
   <si>
@@ -112,15 +118,9 @@
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
     <t>TLAXCALTECATL</t>
   </si>
   <si>
@@ -136,6 +136,12 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -154,12 +160,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -172,6 +172,12 @@
     <t>JOSELIN</t>
   </si>
   <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>MARITZA</t>
   </si>
   <si>
@@ -199,13 +205,7 @@
     <t>GABRIELA ELIZABET</t>
   </si>
   <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
     <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
@@ -1151,7 +1151,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920331</v>
+        <v>21330051920390</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1166,15 +1166,15 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920335</v>
+        <v>21330051920059</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1189,15 +1189,15 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920137</v>
+        <v>21330051920331</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1220,13 +1220,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920336</v>
+        <v>21330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>54</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920340</v>
+        <v>21330051920137</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>55</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920347</v>
+        <v>21330051920336</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920029</v>
+        <v>21330051920340</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1304,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1312,13 +1312,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920031</v>
+        <v>21330051920347</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
@@ -1327,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1335,13 +1335,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920035</v>
+        <v>21330051920029</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
         <v>59</v>
@@ -1358,13 +1358,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920390</v>
+        <v>21330051920031</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
@@ -1381,13 +1381,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920057</v>
+        <v>21330051920035</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920059</v>
+        <v>21330051920057</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
@@ -1433,7 +1433,7 @@
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="78">
   <si>
     <t>Mat</t>
   </si>
@@ -88,12 +88,21 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>ROMANOS</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ABAD</t>
   </si>
   <si>
@@ -103,7 +112,10 @@
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>PEREZ</t>
@@ -130,28 +142,34 @@
     <t>VEGA</t>
   </si>
   <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
     <t>SOL</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>CELESTINO</t>
   </si>
   <si>
     <t>TEZOCO</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>JUAREZ</t>
@@ -166,18 +184,30 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
     <t>JOSELIN</t>
   </si>
   <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
     <t>KARLA JIMENA</t>
   </si>
   <si>
     <t>DANIELA</t>
   </si>
   <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
     <t>MARITZA</t>
   </si>
   <si>
@@ -190,7 +220,10 @@
     <t>YAIR DAVID</t>
   </si>
   <si>
-    <t>DARLET VICTORIA</t>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JOCELIN</t>
   </si>
   <si>
     <t>ANGEL DE JESUS</t>
@@ -215,6 +248,9 @@
   </si>
   <si>
     <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -784,16 +820,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>59.26</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -833,16 +872,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>73.08</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -856,19 +898,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>70.59</v>
+        <v>94.12</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -950,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>59.26</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1002,16 +1044,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>88.45999999999999</v>
+        <v>73.08</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1073,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1111,10 +1153,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1134,10 +1176,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1151,22 +1193,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920390</v>
+        <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1174,16 +1216,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920059</v>
+        <v>21330051920390</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1197,85 +1239,85 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920331</v>
+        <v>21330051920059</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920335</v>
+        <v>20330051920217</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920137</v>
+        <v>20330051920259</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920336</v>
+        <v>21330051920331</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1289,16 +1331,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920340</v>
+        <v>21330051920335</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1312,16 +1354,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920347</v>
+        <v>21330051920137</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1335,22 +1377,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920029</v>
+        <v>21330051920336</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1358,22 +1400,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920031</v>
+        <v>20330051920343</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1381,22 +1423,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920035</v>
+        <v>21330051920345</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1404,22 +1446,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920057</v>
+        <v>21330051920347</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1427,16 +1469,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920062</v>
+        <v>21330051920029</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1450,16 +1492,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920063</v>
+        <v>21330051920031</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1473,16 +1515,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920067</v>
+        <v>21330051920035</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1491,6 +1533,121 @@
         <v>11</v>
       </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920057</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920062</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920063</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920067</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920218</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
   <si>
     <t>Mat</t>
   </si>
@@ -82,76 +82,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AVELLEIRA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>ROMANOS</t>
   </si>
   <si>
+    <t>TLAXCALTECATL</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TLAXCALTECATL</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>CELESTINO</t>
@@ -160,87 +142,42 @@
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
     <t>JOSELIN</t>
   </si>
   <si>
-    <t>ABIGAIL</t>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABET</t>
   </si>
   <si>
     <t>KARLA JIMENA</t>
   </si>
   <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
     <t>DANIELA</t>
   </si>
   <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JOCELIN</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABET</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
     <t>KARLA JAZMIN</t>
   </si>
   <si>
@@ -248,9 +185,6 @@
   </si>
   <si>
     <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -992,16 +926,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>59.26</v>
+        <v>85.19</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1018,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="H3">
         <v>6.3</v>
@@ -1044,16 +978,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>73.08</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1079,7 +1013,7 @@
         <v>94.12</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1096,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H6">
         <v>7.1</v>
@@ -1115,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1147,16 +1081,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920332</v>
+        <v>21330051920149</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1170,22 +1104,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920149</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1193,22 +1127,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920353</v>
+        <v>21330051920048</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1216,114 +1150,114 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920390</v>
+        <v>21330051920137</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920059</v>
+        <v>21330051920347</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920217</v>
+        <v>21330051920029</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920259</v>
+        <v>21330051920035</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920331</v>
+        <v>21330051920390</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1331,22 +1265,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920335</v>
+        <v>21330051920057</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1354,22 +1288,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920137</v>
+        <v>21330051920059</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1377,22 +1311,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920336</v>
+        <v>21330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1400,22 +1334,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920343</v>
+        <v>21330051920063</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1423,231 +1357,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920345</v>
+        <v>21330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920347</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920029</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920031</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920035</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920057</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920062</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920063</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920067</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920218</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20222.xlsx
@@ -88,9 +88,15 @@
     <t>COMIHUA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>VEGA</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
@@ -103,9 +109,6 @@
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -118,15 +121,18 @@
     <t>TETLA</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -136,27 +142,27 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>JOSELIN</t>
   </si>
   <si>
     <t>ALEJANDRO GABRIEL</t>
   </si>
   <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
     <t>MICHEL</t>
   </si>
   <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
     <t>GAEL JARED</t>
   </si>
   <si>
@@ -169,9 +175,6 @@
     <t>GABRIELA ELIZABET</t>
   </si>
   <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
@@ -182,9 +185,6 @@
   </si>
   <si>
     <t>YAZURI</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1087,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>43</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920048</v>
+        <v>21330051920390</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920137</v>
+        <v>21330051920048</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1165,15 +1165,15 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920347</v>
+        <v>21330051920067</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1188,15 +1188,15 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920029</v>
+        <v>21330051920137</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1211,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1219,13 +1219,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920035</v>
+        <v>21330051920347</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
         <v>49</v>
@@ -1234,7 +1234,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1242,13 +1242,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920390</v>
+        <v>21330051920029</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>50</v>
@@ -1265,13 +1265,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920057</v>
+        <v>21330051920035</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920059</v>
+        <v>21330051920057</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920062</v>
+        <v>21330051920059</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -1334,13 +1334,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920063</v>
+        <v>21330051920062</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920067</v>
+        <v>21330051920063</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
